--- a/cats_info.xlsx
+++ b/cats_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/33b815428d211e55/ドキュメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{EEEF4136-C130-7C40-95D8-65B28773EFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1575415C-58A9-E140-9EC3-EA1BAF74AC80}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{EEEF4136-C130-7C40-95D8-65B28773EFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E4C5209-05E4-7E46-A94E-5639821F7053}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15940" xr2:uid="{4B6EC42F-5A7A-E54E-8DCE-59754554E6E0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t>name</t>
     <phoneticPr fontId="1"/>
@@ -91,6 +91,26 @@
   </si>
   <si>
     <t>ひげぴよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイオウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>male</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bonko.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>higepiyo.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>taiou.jpg</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -143,14 +163,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -168,6 +185,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,10 +508,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6E6C02-3F14-0444-B3D5-7CFE310C7B4D}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -518,9 +539,8 @@
       <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -545,8 +565,11 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -570,6 +593,38 @@
       </c>
       <c r="H3" t="b">
         <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
